--- a/OREI Genotyping/3K_MAS_SNPs.xlsx
+++ b/OREI Genotyping/3K_MAS_SNPs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Research\Barley\XTArray\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Siim Sepp\NY_WMBCL\OREI Genotyping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799745D0-6571-4733-81E5-BEAD274EA531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A883CE15-7AD4-4DD1-A601-07D60D5FA487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13245" yWindow="30" windowWidth="29985" windowHeight="15315" xr2:uid="{5756AA9D-1E95-4189-ABC3-E48CAED0EEF7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5756AA9D-1E95-4189-ABC3-E48CAED0EEF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1674,10 +1674,37 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1744,18 +1771,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1772,9 +1804,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1812,7 +1844,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1918,7 +1950,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2060,7 +2092,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2068,23 +2100,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1ABBF9-61F9-449A-9BFA-A84637A8E578}">
-  <dimension ref="A1:K210"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U210"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
-    <col min="7" max="7" width="24.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" customWidth="1"/>
-    <col min="9" max="9" width="63.140625" customWidth="1"/>
-    <col min="10" max="10" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="5"/>
+    <col min="4" max="4" width="9.7265625" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="7" max="7" width="24.1796875" customWidth="1"/>
+    <col min="8" max="8" width="21.1796875" customWidth="1"/>
+    <col min="9" max="9" width="63.1796875" customWidth="1"/>
+    <col min="10" max="10" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1796875" style="4"/>
+    <col min="16" max="16" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>522</v>
       </c>
@@ -2112,14 +2149,14 @@
       <c r="I1" t="s">
         <v>524</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2148,7 +2185,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2177,7 +2214,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -2206,7 +2243,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -2235,7 +2272,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -2264,7 +2301,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -2293,7 +2330,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -2322,7 +2359,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -2351,7 +2388,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>69</v>
       </c>
@@ -2380,7 +2417,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -2409,7 +2446,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>219</v>
       </c>
@@ -2437,8 +2474,14 @@
       <c r="I12" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>225</v>
       </c>
@@ -2466,8 +2509,14 @@
       <c r="I13" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>233</v>
       </c>
@@ -2495,8 +2544,14 @@
       <c r="I14" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>235</v>
       </c>
@@ -2524,8 +2579,14 @@
       <c r="I15" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>247</v>
       </c>
@@ -2553,8 +2614,9 @@
       <c r="I16" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="T16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>263</v>
       </c>
@@ -2583,7 +2645,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>265</v>
       </c>
@@ -2612,7 +2674,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>267</v>
       </c>
@@ -2641,7 +2703,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>295</v>
       </c>
@@ -2670,7 +2732,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>297</v>
       </c>
@@ -2699,7 +2761,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>301</v>
       </c>
@@ -2728,7 +2790,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>303</v>
       </c>
@@ -2757,7 +2819,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>305</v>
       </c>
@@ -2786,7 +2848,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>307</v>
       </c>
@@ -2815,7 +2877,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>309</v>
       </c>
@@ -2844,7 +2906,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>365</v>
       </c>
@@ -2873,7 +2935,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>385</v>
       </c>
@@ -2902,7 +2964,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>417</v>
       </c>
@@ -2931,7 +2993,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>311</v>
       </c>
@@ -2960,7 +3022,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>313</v>
       </c>
@@ -2989,7 +3051,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>315</v>
       </c>
@@ -3018,7 +3080,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>317</v>
       </c>
@@ -3047,7 +3109,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>319</v>
       </c>
@@ -3076,7 +3138,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>323</v>
       </c>
@@ -3105,7 +3167,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>325</v>
       </c>
@@ -3134,7 +3196,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>327</v>
       </c>
@@ -3163,7 +3225,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>329</v>
       </c>
@@ -3192,7 +3254,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>331</v>
       </c>
@@ -3221,7 +3283,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>333</v>
       </c>
@@ -3250,7 +3312,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>387</v>
       </c>
@@ -3279,7 +3341,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>389</v>
       </c>
@@ -3308,7 +3370,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>391</v>
       </c>
@@ -3337,7 +3399,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>393</v>
       </c>
@@ -3366,7 +3428,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>395</v>
       </c>
@@ -3395,7 +3457,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>399</v>
       </c>
@@ -3424,7 +3486,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>401</v>
       </c>
@@ -3453,7 +3515,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>403</v>
       </c>
@@ -3482,7 +3544,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>405</v>
       </c>
@@ -3511,7 +3573,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>407</v>
       </c>
@@ -3540,7 +3602,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>409</v>
       </c>
@@ -3569,7 +3631,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>411</v>
       </c>
@@ -3598,7 +3660,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>413</v>
       </c>
@@ -3627,7 +3689,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>415</v>
       </c>
@@ -3656,7 +3718,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>237</v>
       </c>
@@ -3685,7 +3747,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>239</v>
       </c>
@@ -3714,7 +3776,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>241</v>
       </c>
@@ -3743,7 +3805,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>243</v>
       </c>
@@ -3772,7 +3834,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>245</v>
       </c>
@@ -3801,7 +3863,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -3830,7 +3892,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -3859,7 +3921,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>49</v>
       </c>
@@ -3888,7 +3950,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>73</v>
       </c>
@@ -3917,7 +3979,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>77</v>
       </c>
@@ -3946,7 +4008,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>75</v>
       </c>
@@ -3975,7 +4037,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>79</v>
       </c>
@@ -4004,7 +4066,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>227</v>
       </c>
@@ -4033,7 +4095,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>229</v>
       </c>
@@ -4062,7 +4124,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>231</v>
       </c>
@@ -4091,7 +4153,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>261</v>
       </c>
@@ -4120,7 +4182,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>285</v>
       </c>
@@ -4149,7 +4211,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>287</v>
       </c>
@@ -4178,7 +4240,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>289</v>
       </c>
@@ -4207,7 +4269,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>291</v>
       </c>
@@ -4236,7 +4298,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>321</v>
       </c>
@@ -4265,7 +4327,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>369</v>
       </c>
@@ -4294,7 +4356,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>371</v>
       </c>
@@ -4323,7 +4385,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>383</v>
       </c>
@@ -4352,7 +4414,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>397</v>
       </c>
@@ -4381,7 +4443,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -4410,7 +4472,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -4439,7 +4501,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -4468,7 +4530,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -4497,7 +4559,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -4526,7 +4588,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -4555,7 +4617,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>103</v>
       </c>
@@ -4584,7 +4646,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>117</v>
       </c>
@@ -4613,7 +4675,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>119</v>
       </c>
@@ -4642,7 +4704,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>153</v>
       </c>
@@ -4671,7 +4733,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>163</v>
       </c>
@@ -4700,7 +4762,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>177</v>
       </c>
@@ -4729,7 +4791,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>207</v>
       </c>
@@ -4758,7 +4820,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>209</v>
       </c>
@@ -4787,7 +4849,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>211</v>
       </c>
@@ -4816,7 +4878,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -4845,7 +4907,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>93</v>
       </c>
@@ -4874,7 +4936,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>115</v>
       </c>
@@ -4903,7 +4965,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>121</v>
       </c>
@@ -4932,7 +4994,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>123</v>
       </c>
@@ -4961,7 +5023,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -4990,7 +5052,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>137</v>
       </c>
@@ -5019,7 +5081,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>147</v>
       </c>
@@ -5048,7 +5110,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>149</v>
       </c>
@@ -5077,7 +5139,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>151</v>
       </c>
@@ -5106,7 +5168,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>155</v>
       </c>
@@ -5135,7 +5197,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>169</v>
       </c>
@@ -5164,7 +5226,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>193</v>
       </c>
@@ -5193,7 +5255,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>203</v>
       </c>
@@ -5222,7 +5284,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>205</v>
       </c>
@@ -5251,7 +5313,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>113</v>
       </c>
@@ -5280,7 +5342,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>167</v>
       </c>
@@ -5309,7 +5371,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>197</v>
       </c>
@@ -5338,7 +5400,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>199</v>
       </c>
@@ -5367,7 +5429,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>87</v>
       </c>
@@ -5396,7 +5458,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>95</v>
       </c>
@@ -5425,7 +5487,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>101</v>
       </c>
@@ -5454,7 +5516,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>105</v>
       </c>
@@ -5483,7 +5545,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>135</v>
       </c>
@@ -5512,7 +5574,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -5541,7 +5603,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>141</v>
       </c>
@@ -5570,7 +5632,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>171</v>
       </c>
@@ -5599,7 +5661,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>181</v>
       </c>
@@ -5628,7 +5690,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>189</v>
       </c>
@@ -5657,7 +5719,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>195</v>
       </c>
@@ -5686,7 +5748,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>81</v>
       </c>
@@ -5715,7 +5777,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>83</v>
       </c>
@@ -5744,7 +5806,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>89</v>
       </c>
@@ -5773,7 +5835,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>109</v>
       </c>
@@ -5802,7 +5864,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>111</v>
       </c>
@@ -5831,7 +5893,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>159</v>
       </c>
@@ -5860,7 +5922,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>173</v>
       </c>
@@ -5889,7 +5951,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>191</v>
       </c>
@@ -5918,7 +5980,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>201</v>
       </c>
@@ -5947,7 +6009,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>91</v>
       </c>
@@ -5976,7 +6038,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>157</v>
       </c>
@@ -6005,7 +6067,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>185</v>
       </c>
@@ -6034,7 +6096,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>99</v>
       </c>
@@ -6063,7 +6125,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>107</v>
       </c>
@@ -6092,7 +6154,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>127</v>
       </c>
@@ -6121,7 +6183,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>129</v>
       </c>
@@ -6150,7 +6212,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>131</v>
       </c>
@@ -6179,7 +6241,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>133</v>
       </c>
@@ -6208,7 +6270,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -6237,7 +6299,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>145</v>
       </c>
@@ -6266,7 +6328,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>161</v>
       </c>
@@ -6295,7 +6357,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>165</v>
       </c>
@@ -6324,7 +6386,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -6353,7 +6415,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>179</v>
       </c>
@@ -6382,7 +6444,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>183</v>
       </c>
@@ -6411,7 +6473,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>187</v>
       </c>
@@ -6440,7 +6502,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>213</v>
       </c>
@@ -6469,7 +6531,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>249</v>
       </c>
@@ -6498,7 +6560,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>251</v>
       </c>
@@ -6527,7 +6589,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>253</v>
       </c>
@@ -6556,7 +6618,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>255</v>
       </c>
@@ -6585,7 +6647,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>257</v>
       </c>
@@ -6614,7 +6676,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>259</v>
       </c>
@@ -6643,7 +6705,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>269</v>
       </c>
@@ -6672,7 +6734,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>271</v>
       </c>
@@ -6701,7 +6763,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>293</v>
       </c>
@@ -6730,7 +6792,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>299</v>
       </c>
@@ -6759,7 +6821,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>335</v>
       </c>
@@ -6788,7 +6850,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>337</v>
       </c>
@@ -6817,7 +6879,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>339</v>
       </c>
@@ -6846,7 +6908,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>343</v>
       </c>
@@ -6875,7 +6937,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>345</v>
       </c>
@@ -6904,7 +6966,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>347</v>
       </c>
@@ -6933,7 +6995,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>349</v>
       </c>
@@ -6962,7 +7024,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>351</v>
       </c>
@@ -6991,7 +7053,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>353</v>
       </c>
@@ -7020,7 +7082,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>355</v>
       </c>
@@ -7049,7 +7111,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>359</v>
       </c>
@@ -7078,7 +7140,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>361</v>
       </c>
@@ -7107,7 +7169,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>363</v>
       </c>
@@ -7136,7 +7198,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>367</v>
       </c>
@@ -7165,7 +7227,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>373</v>
       </c>
@@ -7194,7 +7256,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>375</v>
       </c>
@@ -7223,7 +7285,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>377</v>
       </c>
@@ -7252,7 +7314,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>379</v>
       </c>
@@ -7281,8 +7343,8 @@
         <v>510</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="3" t="s">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
         <v>381</v>
       </c>
       <c r="B180" t="s">
@@ -7310,7 +7372,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>22</v>
       </c>
@@ -7339,7 +7401,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>24</v>
       </c>
@@ -7368,7 +7430,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>28</v>
       </c>
@@ -7397,7 +7459,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -7426,7 +7488,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>31</v>
       </c>
@@ -7455,7 +7517,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>33</v>
       </c>
@@ -7484,7 +7546,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>35</v>
       </c>
@@ -7513,7 +7575,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>37</v>
       </c>
@@ -7542,7 +7604,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>41</v>
       </c>
@@ -7571,7 +7633,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>44</v>
       </c>
@@ -7600,7 +7662,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>47</v>
       </c>
@@ -7629,7 +7691,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>51</v>
       </c>
@@ -7658,7 +7720,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>55</v>
       </c>
@@ -7687,7 +7749,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>57</v>
       </c>
@@ -7716,7 +7778,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>53</v>
       </c>
@@ -7745,7 +7807,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>215</v>
       </c>
@@ -7774,7 +7836,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>217</v>
       </c>
@@ -7803,7 +7865,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>221</v>
       </c>
@@ -7832,7 +7894,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>223</v>
       </c>
@@ -7861,7 +7923,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>273</v>
       </c>
@@ -7890,7 +7952,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>275</v>
       </c>
@@ -7919,7 +7981,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>277</v>
       </c>
@@ -7948,7 +8010,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>279</v>
       </c>
@@ -7977,7 +8039,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>281</v>
       </c>
@@ -8006,7 +8068,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>283</v>
       </c>
@@ -8035,7 +8097,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>341</v>
       </c>
@@ -8064,7 +8126,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>357</v>
       </c>
@@ -8093,7 +8155,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>520</v>
       </c>
@@ -8119,7 +8181,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" s="1"/>
     </row>
   </sheetData>
